--- a/competitor_gross_margin_benchmark.xlsx
+++ b/competitor_gross_margin_benchmark.xlsx
@@ -505,6 +505,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -552,15 +553,15 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>FY3/2025</t>
+          <t>FY3/2026</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.106</v>
+        <v>0.125</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>≈ US$38M</t>
+          <t>¥6,825M</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -570,10 +571,11 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Peak 12.8% (FY2017), trough 8.2% (FY2023); EBIT margin 1.7%</t>
-        </is>
-      </c>
-    </row>
+          <t>Recovered from 10.6% (FY3/25); peak 12.8% (FY17), trough 8.2% (FY23); EBIT margin 2.7%; source: audited tanshin May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
@@ -861,6 +863,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
@@ -1210,6 +1213,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
@@ -1220,7 +1224,7 @@
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>1. TBK (10.6%) and Akebono (10.0%) sit at the bottom of the comparable set — half the gross margin of Western brake peers (SAF-Holland ~22%, Cummins 24.7%, Haldex 27.3%).</t>
+          <t>1. TBK (12.5% in FY3/2026, up from 10.6%) and Akebono (10.0%) sit at the bottom of the comparable set — still roughly half the gross margin of Western brake peers (SAF-Holland ~22%, Cummins 24.7%, Haldex 27.3%).</t>
         </is>
       </c>
     </row>

--- a/competitor_gross_margin_benchmark.xlsx
+++ b/competitor_gross_margin_benchmark.xlsx
@@ -1001,27 +1001,25 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>not disclosed ('30%+' unverified)</t>
-        </is>
+          <t>2023 (last public)</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>0.252</v>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MSEK 1,061</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Yes — IFRS cost-of-sales, company-reported (AR2023)</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Operating margin 14.2% (16.7% in 2022) — 8x TBK's EBIT margin</t>
+          <t>2022: 26.3%. Op margin 14.2% (2023) vs 23.5% (2019, pre-EMP) — margin traded for electrification transition</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1236,7 @@
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>3. Pump peers bracket TBK: Hanon 9.1% below, Aisin ~12% just above, TPR ~22% well above. Concentric's 14.2% operating margin vs TBK's 1.7% EBIT margin is the starkest gap.</t>
+          <t>3. Pump peers (incl. Concentric, verified 25.2% per AR2023): Hanon 9.1% below, Aisin ~12% around TBK, TPR ~22% and Concentric 25.2% well above. Comparable pump-panel stats: average 17.0%, median 16.9%.</t>
         </is>
       </c>
     </row>
